--- a/outputs/daily/hr_rankings_2026-08-18_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18_full.xlsx
@@ -52431,27 +52431,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>682622</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-18T22:40:00Z</t>
+          <t>2026-08-18T22:35:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -52461,26 +52461,26 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Carlos Rodón</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>607074</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -52494,26 +52494,26 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>21.9</v>
+        <v>26.9</v>
       </c>
       <c r="Q191" t="n">
-        <v>52.5</v>
+        <v>27</v>
       </c>
       <c r="R191" t="n">
-        <v>39.3</v>
+        <v>32.1</v>
       </c>
       <c r="S191" t="n">
-        <v>59.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T191" t="n">
         <v>50</v>
       </c>
       <c r="U191" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -52569,12 +52569,12 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
@@ -52584,12 +52584,12 @@
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/13, 0 HR</t>
+          <t>Last 7 games: 7/30, 0 HR</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -52599,104 +52599,104 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>99.2453</t>
+          <t>98.2071</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.3382</t>
+          <t>0.3816</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.1296</t>
+          <t>0.1392</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.2571</t>
+          <t>0.3175</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>36.46</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>36.66</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>0.4443</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="BE191" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
       <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -52707,27 +52707,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-18T22:35:00Z</t>
+          <t>2026-08-18T22:40:00Z</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -52737,22 +52737,22 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Carlos Rodón</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>607074</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -52770,26 +52770,26 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>26.9</v>
+        <v>13</v>
       </c>
       <c r="Q192" t="n">
-        <v>27</v>
+        <v>52.5</v>
       </c>
       <c r="R192" t="n">
-        <v>32.1</v>
+        <v>39.3</v>
       </c>
       <c r="S192" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T192" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U192" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -52828,7 +52828,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr"/>
@@ -52845,12 +52845,12 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -52860,12 +52860,12 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/30, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 8.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -52875,104 +52875,104 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>98.2071</t>
+          <t>97.0721</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
         <is>
-          <t>0.3816</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>0.1392</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>0.3175</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>36.46</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>46.62</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.4443</t>
         </is>
       </c>
       <c r="BE192" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
       <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ192" t="inlineStr"/>
